--- a/data/trans_orig/P1410-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2007</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251204</t>
+          <t>251260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264886</t>
+          <t>264986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250055</t>
+          <t>250072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259746</t>
+          <t>259766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>505961</t>
+          <t>506982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522038</t>
+          <t>522964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>44933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>40524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75133</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448708</t>
+          <t>448142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472152</t>
+          <t>471705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464114</t>
+          <t>463425</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484298</t>
+          <t>483832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921891</t>
+          <t>920205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952440</t>
+          <t>952263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297085</t>
+          <t>296150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311536</t>
+          <t>311355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314207</t>
+          <t>313784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329091</t>
+          <t>328583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617885</t>
+          <t>618400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637781</t>
+          <t>638165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15442</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>19565</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>12591</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>29489</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3156</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15016</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>4,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>19565</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12703</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>29413</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339365</t>
+          <t>339634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352509</t>
+          <t>352558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>363309</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>356014</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>368289</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>710562</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>700638</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>717536</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>363309</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>356440</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>368300</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>710562</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>700714</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>717424</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185682</t>
+          <t>185797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198051</t>
+          <t>198095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192565</t>
+          <t>191725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204508</t>
+          <t>204211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383837</t>
+          <t>382385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400230</t>
+          <t>399788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249132</t>
+          <t>248217</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263070</t>
+          <t>263007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266136</t>
+          <t>266096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276057</t>
+          <t>276044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519497</t>
+          <t>519748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537406</t>
+          <t>536822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13156</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30934</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62682</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584093</t>
+          <t>585194</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601871</t>
+          <t>601682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>598518</t>
+          <t>601105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>621590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1190564</t>
+          <t>1190414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1218260</t>
+          <t>1217973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47936</t>
+          <t>47929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>89873</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694108</t>
+          <t>693651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>716973</t>
+          <t>717033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735575</t>
+          <t>735582</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>760208</t>
+          <t>760550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1438596</t>
+          <t>1437433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1471172</t>
+          <t>1470765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130747</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>174841</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>105205</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151020</t>
+          <t>150696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246944</t>
+          <t>244433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>308669</t>
+          <t>310370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3101702</t>
+          <t>3101483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3145796</t>
+          <t>3148036</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3228177</t>
+          <t>3228501</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3273393</t>
+          <t>3273992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6347072</t>
+          <t>6345371</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6408797</t>
+          <t>6411308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2012</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276627</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290166</t>
+          <t>289967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264664</t>
+          <t>265977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280557</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>548229</t>
+          <t>549121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568679</t>
+          <t>567895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32386</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478510</t>
+          <t>480288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496124</t>
+          <t>496319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491379</t>
+          <t>489291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509294</t>
+          <t>508926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977169</t>
+          <t>976373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002081</t>
+          <t>1002744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50104</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296659</t>
+          <t>297305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314631</t>
+          <t>314655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310922</t>
+          <t>311088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328153</t>
+          <t>328457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614962</t>
+          <t>615058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639379</t>
+          <t>639650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32550</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53981</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341432</t>
+          <t>341148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359554</t>
+          <t>359366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360904</t>
+          <t>359459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377672</t>
+          <t>377495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708952</t>
+          <t>709068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734878</t>
+          <t>733230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199284</t>
+          <t>198015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210371</t>
+          <t>210331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199691</t>
+          <t>199759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213337</t>
+          <t>213549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>404307</t>
+          <t>403746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421683</t>
+          <t>421414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>251990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266619</t>
+          <t>266523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249952</t>
+          <t>248702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266413</t>
+          <t>266194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506652</t>
+          <t>507740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529578</t>
+          <t>529805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>42775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>29770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65603</t>
+          <t>64504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>620815</t>
+          <t>620013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642749</t>
+          <t>642054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664380</t>
+          <t>664083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681976</t>
+          <t>682029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1291038</t>
+          <t>1292137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320110</t>
+          <t>1321093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28238</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37016</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750860</t>
+          <t>751354</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767714</t>
+          <t>768467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>784379</t>
+          <t>783699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803929</t>
+          <t>803710</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1540924</t>
+          <t>1542179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1568567</t>
+          <t>1568128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111422</t>
+          <t>111254</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>157498</t>
+          <t>153947</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126734</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>173005</t>
+          <t>174749</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>248326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>316933</t>
+          <t>314820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3269281</t>
+          <t>3272832</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3315357</t>
+          <t>3315525</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3380911</t>
+          <t>3379167</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3428462</t>
+          <t>3427182</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6663761</t>
+          <t>6665874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6734080</t>
+          <t>6732368</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2016</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277583</t>
+          <t>277501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289749</t>
+          <t>289649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268469</t>
+          <t>268168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282761</t>
+          <t>283233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551208</t>
+          <t>551964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569830</t>
+          <t>570255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34661</t>
+          <t>34251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61415</t>
+          <t>62181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472644</t>
+          <t>472856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490191</t>
+          <t>489451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486650</t>
+          <t>486790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506370</t>
+          <t>506440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>964244</t>
+          <t>963478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990998</t>
+          <t>991408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293905</t>
+          <t>293272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308215</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319693</t>
+          <t>318792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332867</t>
+          <t>332597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617874</t>
+          <t>618211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638052</t>
+          <t>638514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49045</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66724</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346726</t>
+          <t>346630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361583</t>
+          <t>361685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338238</t>
+          <t>336827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363486</t>
+          <t>362328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690523</t>
+          <t>690548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720580</t>
+          <t>720669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201244</t>
+          <t>201067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209613</t>
+          <t>209439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208247</t>
+          <t>207742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217500</t>
+          <t>217480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414385</t>
+          <t>414023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425878</t>
+          <t>425524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248972</t>
+          <t>249133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260400</t>
+          <t>260446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248347</t>
+          <t>248105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264761</t>
+          <t>264351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503260</t>
+          <t>503787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523844</t>
+          <t>523675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66740</t>
+          <t>67420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623464</t>
+          <t>623762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642135</t>
+          <t>642140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>652668</t>
+          <t>650369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674247</t>
+          <t>673528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1281112</t>
+          <t>1280432</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1311533</t>
+          <t>1311752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>47421</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>45794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>50556</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84502</t>
+          <t>84530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729403</t>
+          <t>731162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754540</t>
+          <t>754299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780868</t>
+          <t>780373</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803660</t>
+          <t>803446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1520248</t>
+          <t>1520220</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1553703</t>
+          <t>1554194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>104181</t>
+          <t>105577</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149380</t>
+          <t>150123</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>133561</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>184543</t>
+          <t>187856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>253079</t>
+          <t>255287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>320581</t>
+          <t>322397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3244970</t>
+          <t>3244227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3290169</t>
+          <t>3288773</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3359999</t>
+          <t>3356686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3410981</t>
+          <t>3410290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6618311</t>
+          <t>6616495</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6685813</t>
+          <t>6683605</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2023</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289831</t>
+          <t>289247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303200</t>
+          <t>303060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272877</t>
+          <t>271939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283799</t>
+          <t>283547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567501</t>
+          <t>568233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583895</t>
+          <t>584185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>41459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39157</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64557</t>
+          <t>63331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474747</t>
+          <t>474614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496404</t>
+          <t>497817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482062</t>
+          <t>482605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497814</t>
+          <t>497850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965212</t>
+          <t>966438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990612</t>
+          <t>992497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27927</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52695</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288123</t>
+          <t>287794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302589</t>
+          <t>302763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318467</t>
+          <t>319598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332788</t>
+          <t>332763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612483</t>
+          <t>612309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632677</t>
+          <t>632035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49386</t>
+          <t>48338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284563</t>
+          <t>284936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299918</t>
+          <t>299952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448124</t>
+          <t>449235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466252</t>
+          <t>466268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738888</t>
+          <t>739936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764543</t>
+          <t>764798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>168277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>175659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196940</t>
+          <t>197274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203596</t>
+          <t>204018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367768</t>
+          <t>368946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377938</t>
+          <t>377649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240813</t>
+          <t>240350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254868</t>
+          <t>254322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>233133</t>
+          <t>233740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244117</t>
+          <t>244341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478469</t>
+          <t>478951</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496270</t>
+          <t>497030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29792</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>48219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47064</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96315</t>
+          <t>93973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563861</t>
+          <t>564575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593768</t>
+          <t>594081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>800202</t>
+          <t>799669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>835735</t>
+          <t>832863</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375133</t>
+          <t>1377475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424384</t>
+          <t>1426582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>63370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>884720</t>
+          <t>885212</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918399</t>
+          <t>915227</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>686809</t>
+          <t>686789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700207</t>
+          <t>700696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1578263</t>
+          <t>1580742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1612770</t>
+          <t>1615688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>132194</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207281</t>
+          <t>204021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>170024</t>
+          <t>172075</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>283106</t>
+          <t>279511</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>361099</t>
+          <t>363416</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3249500</t>
+          <t>3252760</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3317319</t>
+          <t>3324587</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3485694</t>
+          <t>3483643</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3533997</t>
+          <t>3531387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6751400</t>
+          <t>6749083</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6829393</t>
+          <t>6832988</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1410-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251260</t>
+          <t>251305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264986</t>
+          <t>265111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250072</t>
+          <t>250382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259766</t>
+          <t>259764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506982</t>
+          <t>506519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522964</t>
+          <t>523388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40524</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44761</t>
+          <t>46208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>74831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448142</t>
+          <t>450552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471705</t>
+          <t>472053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463425</t>
+          <t>463719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483832</t>
+          <t>484074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920205</t>
+          <t>922193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952263</t>
+          <t>950816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>21340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296150</t>
+          <t>297506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311355</t>
+          <t>312251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313784</t>
+          <t>315399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328583</t>
+          <t>329121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618400</t>
+          <t>619075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638165</t>
+          <t>637468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29489</t>
+          <t>27433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339634</t>
+          <t>339876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352558</t>
+          <t>352328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356014</t>
+          <t>355791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368289</t>
+          <t>367462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700638</t>
+          <t>702694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717536</t>
+          <t>718042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28591</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185797</t>
+          <t>186308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198095</t>
+          <t>197968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191725</t>
+          <t>192083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204211</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382385</t>
+          <t>382748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399788</t>
+          <t>400403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248217</t>
+          <t>249327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263007</t>
+          <t>263295</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266096</t>
+          <t>265359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276044</t>
+          <t>276048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519748</t>
+          <t>518690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536822</t>
+          <t>537080</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>60237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585194</t>
+          <t>584607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601682</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601105</t>
+          <t>599780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>621590</t>
+          <t>620165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1190414</t>
+          <t>1193009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1217973</t>
+          <t>1218904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50144</t>
+          <t>51136</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56541</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>87402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693651</t>
+          <t>692659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>717033</t>
+          <t>716643</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735582</t>
+          <t>735232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>760550</t>
+          <t>759367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1437433</t>
+          <t>1439904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1470765</t>
+          <t>1471662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>175060</t>
+          <t>176137</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105205</t>
+          <t>106550</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150696</t>
+          <t>149062</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>244433</t>
+          <t>246647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>310370</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3101483</t>
+          <t>3100406</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3148036</t>
+          <t>3148381</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3228501</t>
+          <t>3230135</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3273992</t>
+          <t>3272647</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6345371</t>
+          <t>6346001</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6411308</t>
+          <t>6409094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276180</t>
+          <t>276954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289967</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265977</t>
+          <t>265951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280280</t>
+          <t>280891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549121</t>
+          <t>549383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567895</t>
+          <t>568190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25239</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52919</t>
+          <t>51908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480288</t>
+          <t>479455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496319</t>
+          <t>496499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489291</t>
+          <t>490537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508926</t>
+          <t>510199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976373</t>
+          <t>977384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002744</t>
+          <t>1002280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>49623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297305</t>
+          <t>297596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314655</t>
+          <t>314822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311088</t>
+          <t>311240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328457</t>
+          <t>328420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615058</t>
+          <t>615443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639650</t>
+          <t>639510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>28564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341148</t>
+          <t>340732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359366</t>
+          <t>359622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359459</t>
+          <t>361091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377495</t>
+          <t>377833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709068</t>
+          <t>709824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733230</t>
+          <t>734369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28463</t>
+          <t>27694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198015</t>
+          <t>199315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210331</t>
+          <t>210261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199759</t>
+          <t>199656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213549</t>
+          <t>213562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403746</t>
+          <t>404515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421414</t>
+          <t>421602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>22129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44337</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251990</t>
+          <t>251852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266523</t>
+          <t>266507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248702</t>
+          <t>249093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266194</t>
+          <t>267266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507740</t>
+          <t>507197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529805</t>
+          <t>529411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29770</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64504</t>
+          <t>66020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>620013</t>
+          <t>619530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642054</t>
+          <t>641747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>664083</t>
+          <t>662801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>682029</t>
+          <t>682142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1292137</t>
+          <t>1290621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321093</t>
+          <t>1319441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37696</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751354</t>
+          <t>749835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768467</t>
+          <t>768147</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>783699</t>
+          <t>783657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803710</t>
+          <t>804325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1542179</t>
+          <t>1542585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1568128</t>
+          <t>1569404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>111168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153947</t>
+          <t>157690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>126734</t>
+          <t>125933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>174749</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>248326</t>
+          <t>250073</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>315456</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3272832</t>
+          <t>3269089</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3315525</t>
+          <t>3315611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3379167</t>
+          <t>3379524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3427182</t>
+          <t>3427983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6665874</t>
+          <t>6665238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6732368</t>
+          <t>6730621</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30500</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277501</t>
+          <t>276864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289649</t>
+          <t>289634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268168</t>
+          <t>267749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>283060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551964</t>
+          <t>552388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570255</t>
+          <t>570034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>37591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34251</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62181</t>
+          <t>60486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472856</t>
+          <t>473111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489451</t>
+          <t>490145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486790</t>
+          <t>485493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506440</t>
+          <t>505949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>963478</t>
+          <t>965173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>991408</t>
+          <t>991532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>25445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36663</t>
+          <t>36268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293272</t>
+          <t>293120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307871</t>
+          <t>308576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318792</t>
+          <t>318570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>332666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618211</t>
+          <t>618606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638514</t>
+          <t>638310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23334</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36578</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346630</t>
+          <t>347687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361685</t>
+          <t>361593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336827</t>
+          <t>337061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362328</t>
+          <t>362812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690548</t>
+          <t>690558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720669</t>
+          <t>720538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>201487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209439</t>
+          <t>209607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207742</t>
+          <t>208921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217480</t>
+          <t>217648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414023</t>
+          <t>414126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425524</t>
+          <t>425938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32451</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249133</t>
+          <t>248506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260446</t>
+          <t>260325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248105</t>
+          <t>247296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264351</t>
+          <t>264579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503787</t>
+          <t>503275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523675</t>
+          <t>523099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>64992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623762</t>
+          <t>622694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642140</t>
+          <t>642274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>650369</t>
+          <t>651954</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673528</t>
+          <t>674310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1280432</t>
+          <t>1282860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1311752</t>
+          <t>1311686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50556</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84530</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731162</t>
+          <t>731229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754299</t>
+          <t>754445</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780373</t>
+          <t>780857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803446</t>
+          <t>804907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1520220</t>
+          <t>1520580</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554194</t>
+          <t>1552113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>105577</t>
+          <t>106988</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>150123</t>
+          <t>151519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>134684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>187856</t>
+          <t>187085</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>255287</t>
+          <t>255624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>322397</t>
+          <t>324470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3244227</t>
+          <t>3242831</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3288773</t>
+          <t>3287362</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3356686</t>
+          <t>3357457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3410290</t>
+          <t>3409858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6616495</t>
+          <t>6614422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6683605</t>
+          <t>6683268</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,17 +10767,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>297573</t>
+          <t>303150</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289247</t>
+          <t>295538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303060</t>
+          <t>308981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>279465</t>
+          <t>306368</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271939</t>
+          <t>300616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283547</t>
+          <t>310331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,17 +10880,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>577037</t>
+          <t>609517</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568233</t>
+          <t>600521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584185</t>
+          <t>617104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41459</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>32283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>52104</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>39471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>66129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>487866</t>
+          <t>499713</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474614</t>
+          <t>486890</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497817</t>
+          <t>509384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>491679</t>
+          <t>521666</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482605</t>
+          <t>512921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497850</t>
+          <t>528202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>979545</t>
+          <t>1021378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966438</t>
+          <t>1007353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>992497</t>
+          <t>1034011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516073</t>
+          <t>528279</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516073</t>
+          <t>528279</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516073</t>
+          <t>528279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513696</t>
+          <t>545204</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513696</t>
+          <t>545204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513696</t>
+          <t>545204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029769</t>
+          <t>1073482</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029769</t>
+          <t>1073482</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029769</t>
+          <t>1073482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29530</t>
+          <t>30484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>42189</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52869</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296632</t>
+          <t>296787</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287794</t>
+          <t>288630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302763</t>
+          <t>303158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>326802</t>
+          <t>333398</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>319598</t>
+          <t>325897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332763</t>
+          <t>339796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>623434</t>
+          <t>630186</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612309</t>
+          <t>619582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632035</t>
+          <t>639169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27621</t>
+          <t>29975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48338</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>293879</t>
+          <t>352050</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284936</t>
+          <t>343170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299952</t>
+          <t>358606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>459276</t>
+          <t>404484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449235</t>
+          <t>392580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466268</t>
+          <t>410390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>753154</t>
+          <t>756536</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739936</t>
+          <t>741243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764798</t>
+          <t>766538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172750</t>
+          <t>198970</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168277</t>
+          <t>194156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175659</t>
+          <t>201971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,17 +12217,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>201070</t>
+          <t>219023</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197274</t>
+          <t>214963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204018</t>
+          <t>221909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>373820</t>
+          <t>417992</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368946</t>
+          <t>411818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377649</t>
+          <t>422447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47072</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>248693</t>
+          <t>250162</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240350</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254322</t>
+          <t>256221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>239760</t>
+          <t>246226</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>233740</t>
+          <t>240088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244341</t>
+          <t>250902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>488454</t>
+          <t>496389</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478951</t>
+          <t>487117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497030</t>
+          <t>504470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,17 +12755,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>40727</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29479</t>
+          <t>33222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58985</t>
+          <t>62211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>53071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>88360</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>72042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93973</t>
+          <t>109096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -12868,17 +12868,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>582833</t>
+          <t>671886</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564575</t>
+          <t>656608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594081</t>
+          <t>685597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>815376</t>
+          <t>728589</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>799669</t>
+          <t>716945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>832863</t>
+          <t>738133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1398209</t>
+          <t>1400475</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377475</t>
+          <t>1379739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1426582</t>
+          <t>1416793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847888</t>
+          <t>770016</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847888</t>
+          <t>770016</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847888</t>
+          <t>770016</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471448</t>
+          <t>1488835</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471448</t>
+          <t>1488835</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471448</t>
+          <t>1488835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>44656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63370</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>899596</t>
+          <t>765842</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>885212</t>
+          <t>754049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>915227</t>
+          <t>774066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>694695</t>
+          <t>806971</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>686789</t>
+          <t>798798</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700696</t>
+          <t>813479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1594291</t>
+          <t>1572813</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580742</t>
+          <t>1558719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1615688</t>
+          <t>1584025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132194</t>
+          <t>166361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204021</t>
+          <t>216189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>143315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>172075</t>
+          <t>183498</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>323764</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>363416</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3279821</t>
+          <t>3338561</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3252760</t>
+          <t>3313337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3324587</t>
+          <t>3363165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3508123</t>
+          <t>3566726</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3483643</t>
+          <t>3546256</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3531387</t>
+          <t>3586439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6787944</t>
+          <t>6905287</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6749083</t>
+          <t>6871248</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6832988</t>
+          <t>6935516</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456781</t>
+          <t>3529526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655718</t>
+          <t>3729754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7112499</t>
+          <t>7259280</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
